--- a/3_DELIVERIES/docs/HomeCredit_columns_description.xlsx
+++ b/3_DELIVERIES/docs/HomeCredit_columns_description.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HNg\Desktop\Researches\202507_HOMECREDIT_PD\3_DELIVERIES\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{983297F3-7A23-483D-887F-EF903CA6F83A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55947691-EC01-4F07-B500-958B7E276357}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{61B53BF9-DDD6-49C2-8612-F3C0359008E1}"/>
   </bookViews>
@@ -1813,7 +1813,7 @@
     <xdr:to>
       <xdr:col>18</xdr:col>
       <xdr:colOff>70139</xdr:colOff>
-      <xdr:row>227</xdr:row>
+      <xdr:row>184</xdr:row>
       <xdr:rowOff>179365</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4620,7 +4620,7 @@
       <c r="E143" s="3"/>
       <c r="F143" s="3"/>
     </row>
-    <row r="144" spans="1:6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:6" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
         <v>145</v>
       </c>
@@ -4636,7 +4636,7 @@
       <c r="E144" s="3"/>
       <c r="F144" s="3"/>
     </row>
-    <row r="145" spans="1:6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
         <v>146</v>
       </c>
@@ -4652,7 +4652,7 @@
       <c r="E145" s="3"/>
       <c r="F145" s="3"/>
     </row>
-    <row r="146" spans="1:6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:6" customFormat="1" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
         <v>147</v>
       </c>
@@ -4670,7 +4670,7 @@
       </c>
       <c r="F146" s="3"/>
     </row>
-    <row r="147" spans="1:6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
         <v>148</v>
       </c>
@@ -4686,7 +4686,7 @@
       <c r="E147" s="3"/>
       <c r="F147" s="3"/>
     </row>
-    <row r="148" spans="1:6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
         <v>149</v>
       </c>
@@ -4702,7 +4702,7 @@
       <c r="E148" s="3"/>
       <c r="F148" s="3"/>
     </row>
-    <row r="149" spans="1:6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
         <v>150</v>
       </c>
@@ -4718,7 +4718,7 @@
       <c r="E149" s="3"/>
       <c r="F149" s="3"/>
     </row>
-    <row r="150" spans="1:6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:6" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
         <v>151</v>
       </c>
@@ -4734,7 +4734,7 @@
       <c r="E150" s="3"/>
       <c r="F150" s="3"/>
     </row>
-    <row r="151" spans="1:6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:6" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
         <v>152</v>
       </c>
@@ -5124,7 +5124,7 @@
       <c r="E174" s="3"/>
       <c r="F174" s="3"/>
     </row>
-    <row r="175" spans="1:6" customFormat="1" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A175" s="1">
         <v>176</v>
       </c>
@@ -5142,7 +5142,7 @@
       </c>
       <c r="F175" s="3"/>
     </row>
-    <row r="176" spans="1:6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A176" s="1">
         <v>177</v>
       </c>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="F176" s="3"/>
     </row>
-    <row r="177" spans="1:6" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A177" s="1">
         <v>178</v>
       </c>
@@ -5176,7 +5176,7 @@
       <c r="E177" s="3"/>
       <c r="F177" s="3"/>
     </row>
-    <row r="178" spans="1:6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A178" s="1">
         <v>179</v>
       </c>
@@ -5192,7 +5192,7 @@
       <c r="E178" s="3"/>
       <c r="F178" s="3"/>
     </row>
-    <row r="179" spans="1:6" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A179" s="1">
         <v>180</v>
       </c>
@@ -5208,7 +5208,7 @@
       <c r="E179" s="3"/>
       <c r="F179" s="3"/>
     </row>
-    <row r="180" spans="1:6" customFormat="1" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A180" s="1">
         <v>181</v>
       </c>
@@ -5224,7 +5224,7 @@
       <c r="E180" s="3"/>
       <c r="F180" s="3"/>
     </row>
-    <row r="181" spans="1:6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
         <v>182</v>
       </c>
@@ -5240,7 +5240,7 @@
       <c r="E181" s="3"/>
       <c r="F181" s="3"/>
     </row>
-    <row r="182" spans="1:6" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
         <v>183</v>
       </c>
@@ -5256,7 +5256,7 @@
       <c r="E182" s="3"/>
       <c r="F182" s="3"/>
     </row>
-    <row r="183" spans="1:6" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A183" s="1">
         <v>184</v>
       </c>
@@ -5272,7 +5272,7 @@
       <c r="E183" s="3"/>
       <c r="F183" s="3"/>
     </row>
-    <row r="184" spans="1:6" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A184" s="1">
         <v>185</v>
       </c>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="F184" s="3"/>
     </row>
-    <row r="185" spans="1:6" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
         <v>186</v>
       </c>
@@ -5306,7 +5306,7 @@
       <c r="E185" s="3"/>
       <c r="F185" s="3"/>
     </row>
-    <row r="186" spans="1:6" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
         <v>187</v>
       </c>
@@ -5322,7 +5322,7 @@
       <c r="E186" s="3"/>
       <c r="F186" s="3"/>
     </row>
-    <row r="187" spans="1:6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A187" s="1">
         <v>188</v>
       </c>
@@ -5338,7 +5338,7 @@
       <c r="E187" s="3"/>
       <c r="F187" s="3"/>
     </row>
-    <row r="188" spans="1:6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A188" s="1">
         <v>189</v>
       </c>
@@ -5356,7 +5356,7 @@
       </c>
       <c r="F188" s="3"/>
     </row>
-    <row r="189" spans="1:6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A189" s="1">
         <v>190</v>
       </c>
@@ -5374,7 +5374,7 @@
       </c>
       <c r="F189" s="3"/>
     </row>
-    <row r="190" spans="1:6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
         <v>191</v>
       </c>
@@ -5392,7 +5392,7 @@
       </c>
       <c r="F190" s="3"/>
     </row>
-    <row r="191" spans="1:6" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A191" s="1">
         <v>192</v>
       </c>
@@ -5408,7 +5408,7 @@
       <c r="E191" s="3"/>
       <c r="F191" s="3"/>
     </row>
-    <row r="192" spans="1:6" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A192" s="1">
         <v>193</v>
       </c>
@@ -5424,7 +5424,7 @@
       <c r="E192" s="3"/>
       <c r="F192" s="3"/>
     </row>
-    <row r="193" spans="1:6" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A193" s="1">
         <v>194</v>
       </c>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="F193" s="3"/>
     </row>
-    <row r="194" spans="1:6" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A194" s="1">
         <v>195</v>
       </c>
@@ -5458,7 +5458,7 @@
       <c r="E194" s="3"/>
       <c r="F194" s="3"/>
     </row>
-    <row r="195" spans="1:6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A195" s="1">
         <v>196</v>
       </c>
@@ -5474,7 +5474,7 @@
       <c r="E195" s="3"/>
       <c r="F195" s="3"/>
     </row>
-    <row r="196" spans="1:6" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A196" s="1">
         <v>197</v>
       </c>
@@ -5490,7 +5490,7 @@
       <c r="E196" s="3"/>
       <c r="F196" s="3"/>
     </row>
-    <row r="197" spans="1:6" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A197" s="1">
         <v>198</v>
       </c>
@@ -5506,7 +5506,7 @@
       <c r="E197" s="3"/>
       <c r="F197" s="3"/>
     </row>
-    <row r="198" spans="1:6" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A198" s="1">
         <v>199</v>
       </c>
@@ -5522,7 +5522,7 @@
       <c r="E198" s="3"/>
       <c r="F198" s="3"/>
     </row>
-    <row r="199" spans="1:6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A199" s="1">
         <v>200</v>
       </c>
@@ -5538,7 +5538,7 @@
       <c r="E199" s="3"/>
       <c r="F199" s="3"/>
     </row>
-    <row r="200" spans="1:6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A200" s="1">
         <v>201</v>
       </c>
@@ -5554,7 +5554,7 @@
       <c r="E200" s="3"/>
       <c r="F200" s="3"/>
     </row>
-    <row r="201" spans="1:6" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A201" s="1">
         <v>202</v>
       </c>
@@ -5570,7 +5570,7 @@
       <c r="E201" s="3"/>
       <c r="F201" s="3"/>
     </row>
-    <row r="202" spans="1:6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A202" s="1">
         <v>203</v>
       </c>
@@ -5586,7 +5586,7 @@
       <c r="E202" s="3"/>
       <c r="F202" s="3"/>
     </row>
-    <row r="203" spans="1:6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A203" s="1">
         <v>204</v>
       </c>
@@ -5602,7 +5602,7 @@
       <c r="E203" s="3"/>
       <c r="F203" s="3"/>
     </row>
-    <row r="204" spans="1:6" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A204" s="1">
         <v>205</v>
       </c>
@@ -5618,7 +5618,7 @@
       <c r="E204" s="3"/>
       <c r="F204" s="3"/>
     </row>
-    <row r="205" spans="1:6" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A205" s="1">
         <v>206</v>
       </c>
@@ -5636,7 +5636,7 @@
       </c>
       <c r="F205" s="3"/>
     </row>
-    <row r="206" spans="1:6" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A206" s="1">
         <v>207</v>
       </c>
@@ -5652,7 +5652,7 @@
       <c r="E206" s="3"/>
       <c r="F206" s="3"/>
     </row>
-    <row r="207" spans="1:6" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A207" s="1">
         <v>208</v>
       </c>
@@ -5670,7 +5670,7 @@
       </c>
       <c r="F207" s="3"/>
     </row>
-    <row r="208" spans="1:6" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A208" s="1">
         <v>209</v>
       </c>
@@ -5688,7 +5688,7 @@
       </c>
       <c r="F208" s="3"/>
     </row>
-    <row r="209" spans="1:6" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A209" s="1">
         <v>210</v>
       </c>
@@ -5706,7 +5706,7 @@
       </c>
       <c r="F209" s="3"/>
     </row>
-    <row r="210" spans="1:6" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A210" s="1">
         <v>211</v>
       </c>
@@ -5724,7 +5724,7 @@
       </c>
       <c r="F210" s="3"/>
     </row>
-    <row r="211" spans="1:6" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A211" s="1">
         <v>212</v>
       </c>
@@ -5742,7 +5742,7 @@
       </c>
       <c r="F211" s="3"/>
     </row>
-    <row r="212" spans="1:6" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A212" s="1">
         <v>213</v>
       </c>
@@ -5758,7 +5758,7 @@
       <c r="E212" s="3"/>
       <c r="F212" s="3"/>
     </row>
-    <row r="213" spans="1:6" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A213" s="1">
         <v>214</v>
       </c>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="F213" s="3"/>
     </row>
-    <row r="214" spans="1:6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A214" s="1">
         <v>215</v>
       </c>
@@ -5794,7 +5794,7 @@
       </c>
       <c r="F214" s="3"/>
     </row>
-    <row r="215" spans="1:6" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A215" s="1">
         <v>216</v>
       </c>
@@ -5810,7 +5810,7 @@
       <c r="E215" s="3"/>
       <c r="F215" s="3"/>
     </row>
-    <row r="216" spans="1:6" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A216" s="1">
         <v>217</v>
       </c>
@@ -5826,7 +5826,7 @@
       <c r="E216" s="3"/>
       <c r="F216" s="3"/>
     </row>
-    <row r="217" spans="1:6" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A217" s="1">
         <v>218</v>
       </c>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="F217" s="3"/>
     </row>
-    <row r="218" spans="1:6" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A218" s="1">
         <v>219</v>
       </c>
@@ -5862,7 +5862,7 @@
       </c>
       <c r="F218" s="3"/>
     </row>
-    <row r="219" spans="1:6" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A219" s="1">
         <v>220</v>
       </c>
@@ -5878,7 +5878,7 @@
       <c r="E219" s="3"/>
       <c r="F219" s="3"/>
     </row>
-    <row r="220" spans="1:6" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A220" s="1">
         <v>221</v>
       </c>
@@ -5904,7 +5904,8 @@
   <autoFilter ref="A1:F220" xr:uid="{88CA15A8-75B4-47E1-A8DD-8D971A2FD1A5}">
     <filterColumn colId="1">
       <filters>
-        <filter val="POS_CASH_balance.csv"/>
+        <filter val="installments_payments.csv"/>
+        <filter val="previous_application.csv"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/3_DELIVERIES/docs/HomeCredit_columns_description.xlsx
+++ b/3_DELIVERIES/docs/HomeCredit_columns_description.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HNg\Desktop\Researches\202507_HOMECREDIT_PD\3_DELIVERIES\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55947691-EC01-4F07-B500-958B7E276357}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EB69430-8423-4A18-8F2D-0FDAC363212A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{61B53BF9-DDD6-49C2-8612-F3C0359008E1}"/>
   </bookViews>
@@ -1806,15 +1806,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>277957</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>1731</xdr:rowOff>
+      <xdr:colOff>197360</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>117231</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>70139</xdr:colOff>
-      <xdr:row>184</xdr:row>
-      <xdr:rowOff>179365</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>597677</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>106096</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1844,8 +1844,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="12108007" y="192231"/>
-          <a:ext cx="7107382" cy="4560865"/>
+          <a:off x="11378245" y="117231"/>
+          <a:ext cx="7089797" cy="4560865"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2184,7 +2184,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88CA15A8-75B4-47E1-A8DD-8D971A2FD1A5}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:F228"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2216,7 +2215,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="7">
         <v>1</v>
       </c>
@@ -2234,7 +2233,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="11">
         <v>2</v>
       </c>
@@ -2250,7 +2249,7 @@
       <c r="E3" s="13"/>
       <c r="F3" s="13"/>
     </row>
-    <row r="4" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="14">
         <v>5</v>
       </c>
@@ -2266,7 +2265,7 @@
       <c r="E4" s="16"/>
       <c r="F4" s="16"/>
     </row>
-    <row r="5" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="14">
         <v>6</v>
       </c>
@@ -2282,7 +2281,7 @@
       <c r="E5" s="16"/>
       <c r="F5" s="16"/>
     </row>
-    <row r="6" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="14">
         <v>7</v>
       </c>
@@ -2298,7 +2297,7 @@
       <c r="E6" s="16"/>
       <c r="F6" s="16"/>
     </row>
-    <row r="7" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="14">
         <v>8</v>
       </c>
@@ -2314,7 +2313,7 @@
       <c r="E7" s="16"/>
       <c r="F7" s="16"/>
     </row>
-    <row r="8" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="14">
         <v>9</v>
       </c>
@@ -2330,7 +2329,7 @@
       <c r="E8" s="16"/>
       <c r="F8" s="16"/>
     </row>
-    <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="14">
         <v>10</v>
       </c>
@@ -2346,7 +2345,7 @@
       <c r="E9" s="16"/>
       <c r="F9" s="16"/>
     </row>
-    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="14">
         <v>11</v>
       </c>
@@ -2362,7 +2361,7 @@
       <c r="E10" s="16"/>
       <c r="F10" s="16"/>
     </row>
-    <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="14">
         <v>12</v>
       </c>
@@ -2378,7 +2377,7 @@
       <c r="E11" s="16"/>
       <c r="F11" s="16"/>
     </row>
-    <row r="12" spans="1:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="14">
         <v>13</v>
       </c>
@@ -2394,7 +2393,7 @@
       <c r="E12" s="16"/>
       <c r="F12" s="16"/>
     </row>
-    <row r="13" spans="1:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="14">
         <v>14</v>
       </c>
@@ -2410,7 +2409,7 @@
       <c r="E13" s="16"/>
       <c r="F13" s="16"/>
     </row>
-    <row r="14" spans="1:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="14">
         <v>15</v>
       </c>
@@ -2426,7 +2425,7 @@
       <c r="E14" s="16"/>
       <c r="F14" s="16"/>
     </row>
-    <row r="15" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="14">
         <v>16</v>
       </c>
@@ -2442,7 +2441,7 @@
       <c r="E15" s="16"/>
       <c r="F15" s="16"/>
     </row>
-    <row r="16" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="14">
         <v>17</v>
       </c>
@@ -2458,7 +2457,7 @@
       <c r="E16" s="16"/>
       <c r="F16" s="16"/>
     </row>
-    <row r="17" spans="1:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="14">
         <v>18</v>
       </c>
@@ -2474,7 +2473,7 @@
       <c r="E17" s="16"/>
       <c r="F17" s="16"/>
     </row>
-    <row r="18" spans="1:6" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="14">
         <v>19</v>
       </c>
@@ -2492,7 +2491,7 @@
       </c>
       <c r="F18" s="16"/>
     </row>
-    <row r="19" spans="1:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="14">
         <v>20</v>
       </c>
@@ -2510,7 +2509,7 @@
       </c>
       <c r="F19" s="16"/>
     </row>
-    <row r="20" spans="1:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="14">
         <v>21</v>
       </c>
@@ -2528,7 +2527,7 @@
       </c>
       <c r="F20" s="16"/>
     </row>
-    <row r="21" spans="1:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="14">
         <v>22</v>
       </c>
@@ -2546,7 +2545,7 @@
       </c>
       <c r="F21" s="16"/>
     </row>
-    <row r="22" spans="1:6" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A22" s="14">
         <v>23</v>
       </c>
@@ -2564,7 +2563,7 @@
       </c>
       <c r="F22" s="16"/>
     </row>
-    <row r="23" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="14">
         <v>24</v>
       </c>
@@ -2580,7 +2579,7 @@
       <c r="E23" s="16"/>
       <c r="F23" s="16"/>
     </row>
-    <row r="24" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="14">
         <v>25</v>
       </c>
@@ -2596,7 +2595,7 @@
       <c r="E24" s="16"/>
       <c r="F24" s="16"/>
     </row>
-    <row r="25" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="14">
         <v>26</v>
       </c>
@@ -2612,7 +2611,7 @@
       <c r="E25" s="16"/>
       <c r="F25" s="16"/>
     </row>
-    <row r="26" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="14">
         <v>27</v>
       </c>
@@ -2628,7 +2627,7 @@
       <c r="E26" s="16"/>
       <c r="F26" s="16"/>
     </row>
-    <row r="27" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="14">
         <v>28</v>
       </c>
@@ -2644,7 +2643,7 @@
       <c r="E27" s="16"/>
       <c r="F27" s="16"/>
     </row>
-    <row r="28" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="14">
         <v>29</v>
       </c>
@@ -2660,7 +2659,7 @@
       <c r="E28" s="16"/>
       <c r="F28" s="16"/>
     </row>
-    <row r="29" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="14">
         <v>30</v>
       </c>
@@ -2676,7 +2675,7 @@
       <c r="E29" s="16"/>
       <c r="F29" s="16"/>
     </row>
-    <row r="30" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="14">
         <v>31</v>
       </c>
@@ -2692,7 +2691,7 @@
       <c r="E30" s="16"/>
       <c r="F30" s="16"/>
     </row>
-    <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="14">
         <v>32</v>
       </c>
@@ -2708,7 +2707,7 @@
       <c r="E31" s="16"/>
       <c r="F31" s="16"/>
     </row>
-    <row r="32" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="14">
         <v>33</v>
       </c>
@@ -2724,7 +2723,7 @@
       <c r="E32" s="16"/>
       <c r="F32" s="16"/>
     </row>
-    <row r="33" spans="1:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="14">
         <v>34</v>
       </c>
@@ -2740,7 +2739,7 @@
       <c r="E33" s="16"/>
       <c r="F33" s="16"/>
     </row>
-    <row r="34" spans="1:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="14">
         <v>35</v>
       </c>
@@ -2756,7 +2755,7 @@
       <c r="E34" s="16"/>
       <c r="F34" s="16"/>
     </row>
-    <row r="35" spans="1:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="14">
         <v>36</v>
       </c>
@@ -2774,7 +2773,7 @@
       </c>
       <c r="F35" s="16"/>
     </row>
-    <row r="36" spans="1:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="14">
         <v>37</v>
       </c>
@@ -2790,7 +2789,7 @@
       <c r="E36" s="16"/>
       <c r="F36" s="16"/>
     </row>
-    <row r="37" spans="1:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="14">
         <v>38</v>
       </c>
@@ -2806,7 +2805,7 @@
       <c r="E37" s="16"/>
       <c r="F37" s="16"/>
     </row>
-    <row r="38" spans="1:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="14">
         <v>39</v>
       </c>
@@ -2822,7 +2821,7 @@
       <c r="E38" s="16"/>
       <c r="F38" s="16"/>
     </row>
-    <row r="39" spans="1:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="14">
         <v>40</v>
       </c>
@@ -2838,7 +2837,7 @@
       <c r="E39" s="16"/>
       <c r="F39" s="16"/>
     </row>
-    <row r="40" spans="1:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="14">
         <v>41</v>
       </c>
@@ -2854,7 +2853,7 @@
       <c r="E40" s="16"/>
       <c r="F40" s="16"/>
     </row>
-    <row r="41" spans="1:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A41" s="14">
         <v>42</v>
       </c>
@@ -2870,7 +2869,7 @@
       <c r="E41" s="16"/>
       <c r="F41" s="16"/>
     </row>
-    <row r="42" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="14">
         <v>43</v>
       </c>
@@ -2886,7 +2885,7 @@
       <c r="E42" s="16"/>
       <c r="F42" s="16"/>
     </row>
-    <row r="43" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="14">
         <v>44</v>
       </c>
@@ -2904,7 +2903,7 @@
       </c>
       <c r="F43" s="16"/>
     </row>
-    <row r="44" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="14">
         <v>45</v>
       </c>
@@ -2922,7 +2921,7 @@
       </c>
       <c r="F44" s="16"/>
     </row>
-    <row r="45" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="14">
         <v>46</v>
       </c>
@@ -2940,7 +2939,7 @@
       </c>
       <c r="F45" s="16"/>
     </row>
-    <row r="46" spans="1:6" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A46" s="14">
         <v>47</v>
       </c>
@@ -2958,7 +2957,7 @@
       </c>
       <c r="F46" s="16"/>
     </row>
-    <row r="47" spans="1:6" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A47" s="14">
         <v>48</v>
       </c>
@@ -2976,7 +2975,7 @@
       </c>
       <c r="F47" s="16"/>
     </row>
-    <row r="48" spans="1:6" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A48" s="14">
         <v>49</v>
       </c>
@@ -2994,7 +2993,7 @@
       </c>
       <c r="F48" s="16"/>
     </row>
-    <row r="49" spans="1:6" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A49" s="14">
         <v>50</v>
       </c>
@@ -3012,7 +3011,7 @@
       </c>
       <c r="F49" s="16"/>
     </row>
-    <row r="50" spans="1:6" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A50" s="14">
         <v>51</v>
       </c>
@@ -3030,7 +3029,7 @@
       </c>
       <c r="F50" s="16"/>
     </row>
-    <row r="51" spans="1:6" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A51" s="14">
         <v>52</v>
       </c>
@@ -3048,7 +3047,7 @@
       </c>
       <c r="F51" s="16"/>
     </row>
-    <row r="52" spans="1:6" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A52" s="14">
         <v>53</v>
       </c>
@@ -3066,7 +3065,7 @@
       </c>
       <c r="F52" s="16"/>
     </row>
-    <row r="53" spans="1:6" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A53" s="14">
         <v>54</v>
       </c>
@@ -3084,7 +3083,7 @@
       </c>
       <c r="F53" s="16"/>
     </row>
-    <row r="54" spans="1:6" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A54" s="14">
         <v>55</v>
       </c>
@@ -3102,7 +3101,7 @@
       </c>
       <c r="F54" s="16"/>
     </row>
-    <row r="55" spans="1:6" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A55" s="14">
         <v>56</v>
       </c>
@@ -3120,7 +3119,7 @@
       </c>
       <c r="F55" s="16"/>
     </row>
-    <row r="56" spans="1:6" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A56" s="14">
         <v>57</v>
       </c>
@@ -3138,7 +3137,7 @@
       </c>
       <c r="F56" s="16"/>
     </row>
-    <row r="57" spans="1:6" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A57" s="14">
         <v>58</v>
       </c>
@@ -3156,7 +3155,7 @@
       </c>
       <c r="F57" s="16"/>
     </row>
-    <row r="58" spans="1:6" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A58" s="14">
         <v>59</v>
       </c>
@@ -3174,7 +3173,7 @@
       </c>
       <c r="F58" s="16"/>
     </row>
-    <row r="59" spans="1:6" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A59" s="14">
         <v>60</v>
       </c>
@@ -3192,7 +3191,7 @@
       </c>
       <c r="F59" s="16"/>
     </row>
-    <row r="60" spans="1:6" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A60" s="14">
         <v>61</v>
       </c>
@@ -3210,7 +3209,7 @@
       </c>
       <c r="F60" s="16"/>
     </row>
-    <row r="61" spans="1:6" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A61" s="14">
         <v>62</v>
       </c>
@@ -3228,7 +3227,7 @@
       </c>
       <c r="F61" s="16"/>
     </row>
-    <row r="62" spans="1:6" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A62" s="14">
         <v>63</v>
       </c>
@@ -3246,7 +3245,7 @@
       </c>
       <c r="F62" s="16"/>
     </row>
-    <row r="63" spans="1:6" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A63" s="14">
         <v>64</v>
       </c>
@@ -3264,7 +3263,7 @@
       </c>
       <c r="F63" s="16"/>
     </row>
-    <row r="64" spans="1:6" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A64" s="14">
         <v>65</v>
       </c>
@@ -3282,7 +3281,7 @@
       </c>
       <c r="F64" s="16"/>
     </row>
-    <row r="65" spans="1:6" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A65" s="14">
         <v>66</v>
       </c>
@@ -3300,7 +3299,7 @@
       </c>
       <c r="F65" s="16"/>
     </row>
-    <row r="66" spans="1:6" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A66" s="14">
         <v>67</v>
       </c>
@@ -3318,7 +3317,7 @@
       </c>
       <c r="F66" s="16"/>
     </row>
-    <row r="67" spans="1:6" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A67" s="14">
         <v>68</v>
       </c>
@@ -3336,7 +3335,7 @@
       </c>
       <c r="F67" s="16"/>
     </row>
-    <row r="68" spans="1:6" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A68" s="14">
         <v>69</v>
       </c>
@@ -3354,7 +3353,7 @@
       </c>
       <c r="F68" s="16"/>
     </row>
-    <row r="69" spans="1:6" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A69" s="14">
         <v>70</v>
       </c>
@@ -3372,7 +3371,7 @@
       </c>
       <c r="F69" s="16"/>
     </row>
-    <row r="70" spans="1:6" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A70" s="14">
         <v>71</v>
       </c>
@@ -3390,7 +3389,7 @@
       </c>
       <c r="F70" s="16"/>
     </row>
-    <row r="71" spans="1:6" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A71" s="14">
         <v>72</v>
       </c>
@@ -3408,7 +3407,7 @@
       </c>
       <c r="F71" s="16"/>
     </row>
-    <row r="72" spans="1:6" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A72" s="14">
         <v>73</v>
       </c>
@@ -3426,7 +3425,7 @@
       </c>
       <c r="F72" s="16"/>
     </row>
-    <row r="73" spans="1:6" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A73" s="14">
         <v>74</v>
       </c>
@@ -3444,7 +3443,7 @@
       </c>
       <c r="F73" s="16"/>
     </row>
-    <row r="74" spans="1:6" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A74" s="14">
         <v>75</v>
       </c>
@@ -3462,7 +3461,7 @@
       </c>
       <c r="F74" s="16"/>
     </row>
-    <row r="75" spans="1:6" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A75" s="14">
         <v>76</v>
       </c>
@@ -3480,7 +3479,7 @@
       </c>
       <c r="F75" s="16"/>
     </row>
-    <row r="76" spans="1:6" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A76" s="14">
         <v>77</v>
       </c>
@@ -3498,7 +3497,7 @@
       </c>
       <c r="F76" s="16"/>
     </row>
-    <row r="77" spans="1:6" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A77" s="14">
         <v>78</v>
       </c>
@@ -3516,7 +3515,7 @@
       </c>
       <c r="F77" s="16"/>
     </row>
-    <row r="78" spans="1:6" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A78" s="14">
         <v>79</v>
       </c>
@@ -3534,7 +3533,7 @@
       </c>
       <c r="F78" s="16"/>
     </row>
-    <row r="79" spans="1:6" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A79" s="14">
         <v>80</v>
       </c>
@@ -3552,7 +3551,7 @@
       </c>
       <c r="F79" s="16"/>
     </row>
-    <row r="80" spans="1:6" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A80" s="14">
         <v>81</v>
       </c>
@@ -3570,7 +3569,7 @@
       </c>
       <c r="F80" s="16"/>
     </row>
-    <row r="81" spans="1:6" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A81" s="14">
         <v>82</v>
       </c>
@@ -3588,7 +3587,7 @@
       </c>
       <c r="F81" s="16"/>
     </row>
-    <row r="82" spans="1:6" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A82" s="14">
         <v>83</v>
       </c>
@@ -3606,7 +3605,7 @@
       </c>
       <c r="F82" s="16"/>
     </row>
-    <row r="83" spans="1:6" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A83" s="14">
         <v>84</v>
       </c>
@@ -3624,7 +3623,7 @@
       </c>
       <c r="F83" s="16"/>
     </row>
-    <row r="84" spans="1:6" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A84" s="14">
         <v>85</v>
       </c>
@@ -3642,7 +3641,7 @@
       </c>
       <c r="F84" s="16"/>
     </row>
-    <row r="85" spans="1:6" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A85" s="14">
         <v>86</v>
       </c>
@@ -3660,7 +3659,7 @@
       </c>
       <c r="F85" s="16"/>
     </row>
-    <row r="86" spans="1:6" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A86" s="14">
         <v>87</v>
       </c>
@@ -3678,7 +3677,7 @@
       </c>
       <c r="F86" s="16"/>
     </row>
-    <row r="87" spans="1:6" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A87" s="14">
         <v>88</v>
       </c>
@@ -3696,7 +3695,7 @@
       </c>
       <c r="F87" s="16"/>
     </row>
-    <row r="88" spans="1:6" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A88" s="14">
         <v>89</v>
       </c>
@@ -3714,7 +3713,7 @@
       </c>
       <c r="F88" s="16"/>
     </row>
-    <row r="89" spans="1:6" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A89" s="14">
         <v>90</v>
       </c>
@@ -3732,7 +3731,7 @@
       </c>
       <c r="F89" s="16"/>
     </row>
-    <row r="90" spans="1:6" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A90" s="14">
         <v>91</v>
       </c>
@@ -3750,7 +3749,7 @@
       </c>
       <c r="F90" s="16"/>
     </row>
-    <row r="91" spans="1:6" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A91" s="14">
         <v>92</v>
       </c>
@@ -3768,7 +3767,7 @@
       </c>
       <c r="F91" s="16"/>
     </row>
-    <row r="92" spans="1:6" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A92" s="14">
         <v>93</v>
       </c>
@@ -3786,7 +3785,7 @@
       </c>
       <c r="F92" s="16"/>
     </row>
-    <row r="93" spans="1:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A93" s="14">
         <v>94</v>
       </c>
@@ -3802,7 +3801,7 @@
       <c r="E93" s="16"/>
       <c r="F93" s="16"/>
     </row>
-    <row r="94" spans="1:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A94" s="14">
         <v>95</v>
       </c>
@@ -3818,7 +3817,7 @@
       <c r="E94" s="16"/>
       <c r="F94" s="16"/>
     </row>
-    <row r="95" spans="1:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A95" s="14">
         <v>96</v>
       </c>
@@ -3834,7 +3833,7 @@
       <c r="E95" s="16"/>
       <c r="F95" s="16"/>
     </row>
-    <row r="96" spans="1:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A96" s="14">
         <v>97</v>
       </c>
@@ -3850,7 +3849,7 @@
       <c r="E96" s="16"/>
       <c r="F96" s="16"/>
     </row>
-    <row r="97" spans="1:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A97" s="14">
         <v>98</v>
       </c>
@@ -3866,7 +3865,7 @@
       <c r="E97" s="16"/>
       <c r="F97" s="16"/>
     </row>
-    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="14">
         <v>99</v>
       </c>
@@ -3882,7 +3881,7 @@
       <c r="E98" s="16"/>
       <c r="F98" s="16"/>
     </row>
-    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="14">
         <v>100</v>
       </c>
@@ -3898,7 +3897,7 @@
       <c r="E99" s="16"/>
       <c r="F99" s="16"/>
     </row>
-    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="14">
         <v>101</v>
       </c>
@@ -3914,7 +3913,7 @@
       <c r="E100" s="16"/>
       <c r="F100" s="16"/>
     </row>
-    <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="14">
         <v>102</v>
       </c>
@@ -3930,7 +3929,7 @@
       <c r="E101" s="16"/>
       <c r="F101" s="16"/>
     </row>
-    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="14">
         <v>103</v>
       </c>
@@ -3946,7 +3945,7 @@
       <c r="E102" s="16"/>
       <c r="F102" s="16"/>
     </row>
-    <row r="103" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="14">
         <v>104</v>
       </c>
@@ -3962,7 +3961,7 @@
       <c r="E103" s="16"/>
       <c r="F103" s="16"/>
     </row>
-    <row r="104" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="14">
         <v>105</v>
       </c>
@@ -3978,7 +3977,7 @@
       <c r="E104" s="16"/>
       <c r="F104" s="16"/>
     </row>
-    <row r="105" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="14">
         <v>106</v>
       </c>
@@ -3994,7 +3993,7 @@
       <c r="E105" s="16"/>
       <c r="F105" s="16"/>
     </row>
-    <row r="106" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="14">
         <v>107</v>
       </c>
@@ -4010,7 +4009,7 @@
       <c r="E106" s="16"/>
       <c r="F106" s="16"/>
     </row>
-    <row r="107" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="14">
         <v>108</v>
       </c>
@@ -4026,7 +4025,7 @@
       <c r="E107" s="16"/>
       <c r="F107" s="16"/>
     </row>
-    <row r="108" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="14">
         <v>109</v>
       </c>
@@ -4042,7 +4041,7 @@
       <c r="E108" s="16"/>
       <c r="F108" s="16"/>
     </row>
-    <row r="109" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="14">
         <v>110</v>
       </c>
@@ -4058,7 +4057,7 @@
       <c r="E109" s="16"/>
       <c r="F109" s="16"/>
     </row>
-    <row r="110" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="14">
         <v>111</v>
       </c>
@@ -4074,7 +4073,7 @@
       <c r="E110" s="16"/>
       <c r="F110" s="16"/>
     </row>
-    <row r="111" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="14">
         <v>112</v>
       </c>
@@ -4090,7 +4089,7 @@
       <c r="E111" s="16"/>
       <c r="F111" s="16"/>
     </row>
-    <row r="112" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="14">
         <v>113</v>
       </c>
@@ -4106,7 +4105,7 @@
       <c r="E112" s="16"/>
       <c r="F112" s="16"/>
     </row>
-    <row r="113" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="14">
         <v>114</v>
       </c>
@@ -4122,7 +4121,7 @@
       <c r="E113" s="16"/>
       <c r="F113" s="16"/>
     </row>
-    <row r="114" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="14">
         <v>115</v>
       </c>
@@ -4138,7 +4137,7 @@
       <c r="E114" s="16"/>
       <c r="F114" s="16"/>
     </row>
-    <row r="115" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="14">
         <v>116</v>
       </c>
@@ -4154,7 +4153,7 @@
       <c r="E115" s="16"/>
       <c r="F115" s="16"/>
     </row>
-    <row r="116" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="14">
         <v>117</v>
       </c>
@@ -4170,7 +4169,7 @@
       <c r="E116" s="16"/>
       <c r="F116" s="16"/>
     </row>
-    <row r="117" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="14">
         <v>118</v>
       </c>
@@ -4186,7 +4185,7 @@
       <c r="E117" s="16"/>
       <c r="F117" s="16"/>
     </row>
-    <row r="118" spans="1:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A118" s="14">
         <v>119</v>
       </c>
@@ -4202,7 +4201,7 @@
       <c r="E118" s="16"/>
       <c r="F118" s="16"/>
     </row>
-    <row r="119" spans="1:6" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A119" s="14">
         <v>120</v>
       </c>
@@ -4218,7 +4217,7 @@
       <c r="E119" s="16"/>
       <c r="F119" s="16"/>
     </row>
-    <row r="120" spans="1:6" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A120" s="14">
         <v>121</v>
       </c>
@@ -4234,7 +4233,7 @@
       <c r="E120" s="16"/>
       <c r="F120" s="16"/>
     </row>
-    <row r="121" spans="1:6" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A121" s="14">
         <v>122</v>
       </c>
@@ -4250,7 +4249,7 @@
       <c r="E121" s="16"/>
       <c r="F121" s="16"/>
     </row>
-    <row r="122" spans="1:6" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A122" s="14">
         <v>123</v>
       </c>
@@ -4266,7 +4265,7 @@
       <c r="E122" s="16"/>
       <c r="F122" s="16"/>
     </row>
-    <row r="123" spans="1:6" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A123" s="14">
         <v>124</v>
       </c>
@@ -4282,7 +4281,7 @@
       <c r="E123" s="16"/>
       <c r="F123" s="16"/>
     </row>
-    <row r="124" spans="1:6" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>125</v>
       </c>
@@ -4300,7 +4299,7 @@
       </c>
       <c r="F124" s="3"/>
     </row>
-    <row r="125" spans="1:6" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>126</v>
       </c>
@@ -4318,7 +4317,7 @@
       </c>
       <c r="F125" s="3"/>
     </row>
-    <row r="126" spans="1:6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>127</v>
       </c>
@@ -4334,7 +4333,7 @@
       <c r="E126" s="3"/>
       <c r="F126" s="3"/>
     </row>
-    <row r="127" spans="1:6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>128</v>
       </c>
@@ -4352,7 +4351,7 @@
       </c>
       <c r="F127" s="3"/>
     </row>
-    <row r="128" spans="1:6" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>129</v>
       </c>
@@ -4370,7 +4369,7 @@
       </c>
       <c r="F128" s="3"/>
     </row>
-    <row r="129" spans="1:6" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>130</v>
       </c>
@@ -4386,7 +4385,7 @@
       <c r="E129" s="3"/>
       <c r="F129" s="3"/>
     </row>
-    <row r="130" spans="1:6" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>131</v>
       </c>
@@ -4404,7 +4403,7 @@
       </c>
       <c r="F130" s="3"/>
     </row>
-    <row r="131" spans="1:6" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>132</v>
       </c>
@@ -4422,7 +4421,7 @@
       </c>
       <c r="F131" s="3"/>
     </row>
-    <row r="132" spans="1:6" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <v>133</v>
       </c>
@@ -4438,7 +4437,7 @@
       <c r="E132" s="3"/>
       <c r="F132" s="3"/>
     </row>
-    <row r="133" spans="1:6" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>134</v>
       </c>
@@ -4454,7 +4453,7 @@
       <c r="E133" s="3"/>
       <c r="F133" s="3"/>
     </row>
-    <row r="134" spans="1:6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>135</v>
       </c>
@@ -4470,7 +4469,7 @@
       <c r="E134" s="3"/>
       <c r="F134" s="3"/>
     </row>
-    <row r="135" spans="1:6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>136</v>
       </c>
@@ -4486,7 +4485,7 @@
       <c r="E135" s="3"/>
       <c r="F135" s="3"/>
     </row>
-    <row r="136" spans="1:6" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>137</v>
       </c>
@@ -4502,7 +4501,7 @@
       <c r="E136" s="3"/>
       <c r="F136" s="3"/>
     </row>
-    <row r="137" spans="1:6" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <v>138</v>
       </c>
@@ -4518,7 +4517,7 @@
       <c r="E137" s="3"/>
       <c r="F137" s="3"/>
     </row>
-    <row r="138" spans="1:6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>139</v>
       </c>
@@ -4534,7 +4533,7 @@
       <c r="E138" s="3"/>
       <c r="F138" s="3"/>
     </row>
-    <row r="139" spans="1:6" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <v>140</v>
       </c>
@@ -4552,7 +4551,7 @@
       </c>
       <c r="F139" s="3"/>
     </row>
-    <row r="140" spans="1:6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
         <v>141</v>
       </c>
@@ -4568,7 +4567,7 @@
       <c r="E140" s="3"/>
       <c r="F140" s="3"/>
     </row>
-    <row r="141" spans="1:6" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
         <v>142</v>
       </c>
@@ -4586,7 +4585,7 @@
       </c>
       <c r="F141" s="3"/>
     </row>
-    <row r="142" spans="1:6" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <v>143</v>
       </c>
@@ -4604,7 +4603,7 @@
       </c>
       <c r="F142" s="3"/>
     </row>
-    <row r="143" spans="1:6" customFormat="1" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
         <v>144</v>
       </c>
@@ -4620,7 +4619,7 @@
       <c r="E143" s="3"/>
       <c r="F143" s="3"/>
     </row>
-    <row r="144" spans="1:6" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
         <v>145</v>
       </c>
@@ -4636,7 +4635,7 @@
       <c r="E144" s="3"/>
       <c r="F144" s="3"/>
     </row>
-    <row r="145" spans="1:6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
         <v>146</v>
       </c>
@@ -4652,7 +4651,7 @@
       <c r="E145" s="3"/>
       <c r="F145" s="3"/>
     </row>
-    <row r="146" spans="1:6" customFormat="1" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
         <v>147</v>
       </c>
@@ -4670,7 +4669,7 @@
       </c>
       <c r="F146" s="3"/>
     </row>
-    <row r="147" spans="1:6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
         <v>148</v>
       </c>
@@ -4686,7 +4685,7 @@
       <c r="E147" s="3"/>
       <c r="F147" s="3"/>
     </row>
-    <row r="148" spans="1:6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
         <v>149</v>
       </c>
@@ -4702,7 +4701,7 @@
       <c r="E148" s="3"/>
       <c r="F148" s="3"/>
     </row>
-    <row r="149" spans="1:6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
         <v>150</v>
       </c>
@@ -4718,7 +4717,7 @@
       <c r="E149" s="3"/>
       <c r="F149" s="3"/>
     </row>
-    <row r="150" spans="1:6" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
         <v>151</v>
       </c>
@@ -4734,7 +4733,7 @@
       <c r="E150" s="3"/>
       <c r="F150" s="3"/>
     </row>
-    <row r="151" spans="1:6" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
         <v>152</v>
       </c>
@@ -4750,7 +4749,7 @@
       <c r="E151" s="3"/>
       <c r="F151" s="3"/>
     </row>
-    <row r="152" spans="1:6" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
         <v>153</v>
       </c>
@@ -4768,7 +4767,7 @@
       </c>
       <c r="F152" s="3"/>
     </row>
-    <row r="153" spans="1:6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
         <v>154</v>
       </c>
@@ -4786,7 +4785,7 @@
       </c>
       <c r="F153" s="3"/>
     </row>
-    <row r="154" spans="1:6" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
         <v>155</v>
       </c>
@@ -4804,7 +4803,7 @@
       </c>
       <c r="F154" s="3"/>
     </row>
-    <row r="155" spans="1:6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
         <v>156</v>
       </c>
@@ -4820,7 +4819,7 @@
       <c r="E155" s="3"/>
       <c r="F155" s="3"/>
     </row>
-    <row r="156" spans="1:6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
         <v>157</v>
       </c>
@@ -4836,7 +4835,7 @@
       <c r="E156" s="3"/>
       <c r="F156" s="3"/>
     </row>
-    <row r="157" spans="1:6" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
         <v>158</v>
       </c>
@@ -4852,7 +4851,7 @@
       <c r="E157" s="3"/>
       <c r="F157" s="3"/>
     </row>
-    <row r="158" spans="1:6" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
         <v>159</v>
       </c>
@@ -4868,7 +4867,7 @@
       <c r="E158" s="3"/>
       <c r="F158" s="3"/>
     </row>
-    <row r="159" spans="1:6" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
         <v>160</v>
       </c>
@@ -4884,7 +4883,7 @@
       <c r="E159" s="3"/>
       <c r="F159" s="3"/>
     </row>
-    <row r="160" spans="1:6" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
         <v>161</v>
       </c>
@@ -4900,7 +4899,7 @@
       <c r="E160" s="3"/>
       <c r="F160" s="3"/>
     </row>
-    <row r="161" spans="1:6" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
         <v>162</v>
       </c>
@@ -4916,7 +4915,7 @@
       <c r="E161" s="3"/>
       <c r="F161" s="3"/>
     </row>
-    <row r="162" spans="1:6" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
         <v>163</v>
       </c>
@@ -4932,7 +4931,7 @@
       <c r="E162" s="3"/>
       <c r="F162" s="3"/>
     </row>
-    <row r="163" spans="1:6" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
         <v>164</v>
       </c>
@@ -4948,7 +4947,7 @@
       <c r="E163" s="3"/>
       <c r="F163" s="3"/>
     </row>
-    <row r="164" spans="1:6" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
         <v>165</v>
       </c>
@@ -4964,7 +4963,7 @@
       <c r="E164" s="3"/>
       <c r="F164" s="3"/>
     </row>
-    <row r="165" spans="1:6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
         <v>166</v>
       </c>
@@ -4980,7 +4979,7 @@
       <c r="E165" s="3"/>
       <c r="F165" s="3"/>
     </row>
-    <row r="166" spans="1:6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
         <v>167</v>
       </c>
@@ -4996,7 +4995,7 @@
       <c r="E166" s="3"/>
       <c r="F166" s="3"/>
     </row>
-    <row r="167" spans="1:6" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
         <v>168</v>
       </c>
@@ -5012,7 +5011,7 @@
       <c r="E167" s="3"/>
       <c r="F167" s="3"/>
     </row>
-    <row r="168" spans="1:6" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
         <v>169</v>
       </c>
@@ -5028,7 +5027,7 @@
       <c r="E168" s="3"/>
       <c r="F168" s="3"/>
     </row>
-    <row r="169" spans="1:6" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
         <v>170</v>
       </c>
@@ -5044,7 +5043,7 @@
       <c r="E169" s="3"/>
       <c r="F169" s="3"/>
     </row>
-    <row r="170" spans="1:6" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
         <v>171</v>
       </c>
@@ -5060,7 +5059,7 @@
       <c r="E170" s="3"/>
       <c r="F170" s="3"/>
     </row>
-    <row r="171" spans="1:6" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
         <v>172</v>
       </c>
@@ -5076,7 +5075,7 @@
       <c r="E171" s="3"/>
       <c r="F171" s="3"/>
     </row>
-    <row r="172" spans="1:6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
         <v>173</v>
       </c>
@@ -5092,7 +5091,7 @@
       <c r="E172" s="3"/>
       <c r="F172" s="3"/>
     </row>
-    <row r="173" spans="1:6" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
         <v>174</v>
       </c>
@@ -5108,7 +5107,7 @@
       <c r="E173" s="3"/>
       <c r="F173" s="3"/>
     </row>
-    <row r="174" spans="1:6" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
         <v>175</v>
       </c>
@@ -5901,14 +5900,7 @@
       <c r="D228" s="19"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F220" xr:uid="{88CA15A8-75B4-47E1-A8DD-8D971A2FD1A5}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="installments_payments.csv"/>
-        <filter val="previous_application.csv"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:F220" xr:uid="{88CA15A8-75B4-47E1-A8DD-8D971A2FD1A5}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
